--- a/document/成果物ドキュメント_ログイン機能.xlsx
+++ b/document/成果物ドキュメント_ログイン機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFB7B9A-D8AD-435D-B2F9-F45F0E25BEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0723560A-147D-4834-A018-6E7288CDD8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1428,53 +1428,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1482,37 +1446,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1524,11 +1458,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1539,11 +1491,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1557,32 +1515,35 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1593,16 +1554,70 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1611,29 +1626,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1838,23 +1838,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>136071</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>315058</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>40821</xdr:rowOff>
+      <xdr:rowOff>117230</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>367392</xdr:colOff>
+      <xdr:colOff>91829</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>122157</xdr:rowOff>
+      <xdr:rowOff>108856</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74CF9352-1221-AD64-7382-BF33848FDBC2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73407F21-3B5E-8E5D-46C6-EE640C61E1D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1877,8 +1877,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="476250" y="966107"/>
-          <a:ext cx="5374821" cy="5306479"/>
+          <a:off x="315058" y="1042516"/>
+          <a:ext cx="5260450" cy="5216769"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2239,85 +2239,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2337,46 +2337,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="70"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="81" t="s">
+      <c r="H13" s="67"/>
+      <c r="I13" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="67"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="81"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="67"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="81"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="45"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="67"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2385,13 +2385,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3405,19 +3405,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3429,194 +3429,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="80">
+      <c r="G2" s="62"/>
+      <c r="H2" s="43">
         <v>46121</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="49"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="86" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="65"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="88"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="47"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="75"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="47"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="75"/>
     </row>
     <row r="9" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="87" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="47"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="75"/>
     </row>
     <row r="10" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A10" s="96"/>
-      <c r="B10" s="98" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="87" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="47"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="75"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="97"/>
-      <c r="B11" s="98" t="s">
+      <c r="A11" s="84"/>
+      <c r="B11" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="47"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="75"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="47"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="75"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="51" t="s">
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="52"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="86"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4607,17 +4607,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4626,14 +4623,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4652,19 +4652,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4676,48 +4676,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="80">
+      <c r="G2" s="62"/>
+      <c r="H2" s="43">
         <v>46120</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="49"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6072,19 +6072,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6096,48 +6096,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="80">
+      <c r="G2" s="62"/>
+      <c r="H2" s="43">
         <v>46121</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="49"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6290,7 +6290,6 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
@@ -7488,19 +7487,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7512,191 +7511,191 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="80">
+      <c r="G2" s="62"/>
+      <c r="H2" s="43">
         <v>46121</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="64" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="65"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="88"/>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="68"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="69"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="71"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="98"/>
       <c r="K8" s="40"/>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="69"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="71"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="71"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="69"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="71"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="69"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="71"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="69"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="71"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="75"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -7705,11 +7704,11 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="67"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -7722,18 +7721,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="56" t="s">
+      <c r="H16" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="47"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="75"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
       <c r="D17" s="17" t="s">
         <v>92</v>
       </c>
@@ -7751,11 +7750,11 @@
       <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="93" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="45"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="67"/>
       <c r="D18" s="17" t="s">
         <v>90</v>
       </c>
@@ -7773,11 +7772,11 @@
       <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="45"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
       <c r="D19" s="17" t="s">
         <v>93</v>
       </c>
@@ -7788,18 +7787,18 @@
       <c r="G19" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="46" t="s">
+      <c r="H19" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="I19" s="53"/>
-      <c r="J19" s="54"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="101"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="67"/>
       <c r="D20" s="17" t="s">
         <v>95</v>
       </c>
@@ -7810,47 +7809,47 @@
       <c r="G20" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="46" t="s">
+      <c r="H20" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="I20" s="53"/>
-      <c r="J20" s="54"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="101"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
+      <c r="A21" s="93"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="101"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="67"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="47"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="75"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="48"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="52"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="86"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8831,11 +8830,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8852,14 +8854,11 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8884,19 +8883,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="60"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -8908,191 +8907,191 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="62"/>
+      <c r="F2" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="80">
+      <c r="G2" s="62"/>
+      <c r="H2" s="43">
         <v>46121</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="59"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="48"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="60"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="64" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="65"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="88"/>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="75"/>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="66"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="68"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="69"/>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="71"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="98"/>
       <c r="K8" s="40"/>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="69"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="71"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="71"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="69"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="71"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="69"/>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="71"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="69"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="71"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="75"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -9101,11 +9100,11 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="67"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -9118,18 +9117,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="56" t="s">
+      <c r="H16" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="47"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="75"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
       <c r="D17" s="17" t="s">
         <v>101</v>
       </c>
@@ -9147,9 +9146,9 @@
       <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="45"/>
+      <c r="A18" s="93"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="67"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
@@ -9159,64 +9158,64 @@
       <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="93"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="54"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="101"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
+      <c r="A20" s="93"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="67"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="54"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="101"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
+      <c r="A21" s="93"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="101"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="67"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="47"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="75"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="48"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="52"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="86"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10197,6 +10196,19 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
@@ -10213,19 +10225,6 @@
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10245,182 +10244,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="60"/>
+      <c r="Q1" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="60"/>
+      <c r="S1" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="65"/>
+      <c r="T1" s="88"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="68"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="97"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="69"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="71"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="98"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="92"/>
-      <c r="S4" s="101"/>
-      <c r="T4" s="110"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="106"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="86" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
-      <c r="P5" s="62"/>
-      <c r="Q5" s="62"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="65"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="88"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="47"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="75"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="47"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+      <c r="T7" s="75"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10619,37 +10618,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="45"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="56" t="s">
+      <c r="D15" s="67"/>
+      <c r="E15" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="56" t="s">
+      <c r="F15" s="67"/>
+      <c r="G15" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="56" t="s">
+      <c r="H15" s="66"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="56" t="s">
+      <c r="K15" s="67"/>
+      <c r="L15" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="56" t="s">
+      <c r="M15" s="66"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="45"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="67"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -10661,37 +10660,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="102">
+      <c r="A16" s="107">
         <v>1</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="103" t="s">
+      <c r="B16" s="67"/>
+      <c r="C16" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="103" t="s">
+      <c r="D16" s="67"/>
+      <c r="E16" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="108" t="s">
+      <c r="F16" s="67"/>
+      <c r="G16" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="108" t="s">
+      <c r="H16" s="66"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="45"/>
-      <c r="L16" s="106" t="s">
+      <c r="K16" s="67"/>
+      <c r="L16" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="44"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="106" t="s">
+      <c r="M16" s="66"/>
+      <c r="N16" s="67"/>
+      <c r="O16" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="45"/>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="67"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -10703,37 +10702,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="102">
+      <c r="A17" s="107">
         <v>2</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="103" t="s">
+      <c r="B17" s="67"/>
+      <c r="C17" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="103" t="s">
+      <c r="D17" s="67"/>
+      <c r="E17" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="108" t="s">
+      <c r="F17" s="67"/>
+      <c r="G17" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="108" t="s">
+      <c r="H17" s="66"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="45"/>
-      <c r="L17" s="106" t="s">
+      <c r="K17" s="67"/>
+      <c r="L17" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="44"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="106" t="s">
+      <c r="M17" s="66"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="45"/>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="67"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -10745,23 +10744,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="106"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="45"/>
+      <c r="A18" s="107"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="67"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -10773,23 +10772,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="45"/>
+      <c r="A19" s="107"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="66"/>
+      <c r="Q19" s="67"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -10801,23 +10800,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="45"/>
+      <c r="A20" s="107"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="66"/>
+      <c r="Q20" s="67"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -10829,23 +10828,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="45"/>
+      <c r="A21" s="107"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="104"/>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="67"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -10857,23 +10856,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="45"/>
+      <c r="A22" s="107"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="104"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="67"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -10885,23 +10884,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="45"/>
+      <c r="A23" s="107"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="67"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -10913,23 +10912,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="106"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="45"/>
+      <c r="A24" s="107"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="67"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -10941,23 +10940,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="45"/>
+      <c r="A25" s="107"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="67"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -10969,23 +10968,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="45"/>
+      <c r="A26" s="107"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="66"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="67"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -10997,23 +10996,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="45"/>
+      <c r="A27" s="107"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="66"/>
+      <c r="Q27" s="67"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -11025,23 +11024,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="107"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="66"/>
+      <c r="Q28" s="67"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -11053,23 +11052,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="106"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="45"/>
+      <c r="A29" s="107"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="104"/>
+      <c r="P29" s="66"/>
+      <c r="Q29" s="67"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -11081,23 +11080,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="106"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="45"/>
+      <c r="A30" s="107"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="67"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="66"/>
+      <c r="Q30" s="67"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -11109,23 +11108,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="104"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="107"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="50"/>
+      <c r="A31" s="110"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="103"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="78"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="77"/>
+      <c r="Q31" s="78"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -12123,62 +12122,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12203,62 +12202,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_ログイン機能.xlsx
+++ b/document/成果物ドキュメント_ログイン機能.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0723560A-147D-4834-A018-6E7288CDD8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976AAFF4-9B4E-40F7-8F59-F91557380F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -347,25 +347,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.ユーザーがログイン画面を開く
-2.ユーザーがユーザIDとパスワードを入力する
-3.ユーザーが「ログイン」ボタンを押下する
-4.システムがユーザーIDとパスワードを認証に成功する
-5.システムがメニュー画面を表示する</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>4a.ユーザーが入力したユーザーIDとパスワードの片方、または両方が間違っていた場合
-4a1.システムがユーザーIDとパスワードの認証に失敗する
-4a2.システムが認証失敗画面にて「ログインに失敗しました。」と表示する
-4a3.ユーザーが「ログイン画面へ」ボタンを押下する
-4a4.基本フロー1.へ</t>
-    <rPh sb="96" eb="98">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>TaskManager</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -531,6 +512,34 @@
   </si>
   <si>
     <t>LoginServlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.システムがログイン画面を表示する
+2.ユーザーがユーザーIDとパスワードを入力する
+3.ユーザーがログインを選択する
+4.システムがユーザーIDとパスワードを認証に成功する
+5.システムがメニュー画面を表示する</t>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>4a.ユーザーが入力したユーザーIDとパスワードの片方、または両方が間違っていた場合
+4a1.システムがユーザーIDとパスワードの認証に失敗する
+4a2.システムが認証失敗画面にて「ログインに失敗しました。」と表示する
+4a3.ユーザーがログイン画面へを選択する
+4a4.基本フロー1.へ</t>
+    <rPh sb="96" eb="98">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>センタク</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1515,11 +1524,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1527,11 +1548,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1542,8 +1563,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1554,20 +1575,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1576,9 +1594,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1599,17 +1614,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1617,23 +1632,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2338,7 +2347,7 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="71" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F8" s="54"/>
       <c r="G8" s="54"/>
@@ -3405,7 +3414,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="83" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="51"/>
@@ -3473,28 +3482,28 @@
       <c r="J4" s="49"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="81"/>
+      <c r="B5" s="76"/>
       <c r="C5" s="60"/>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="88"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="85" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="67"/>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="78" t="s">
         <v>69</v>
       </c>
       <c r="E6" s="66"/>
@@ -3502,15 +3511,15 @@
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
       <c r="I6" s="66"/>
-      <c r="J6" s="75"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="85" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="67"/>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="78" t="s">
         <v>75</v>
       </c>
       <c r="E7" s="66"/>
@@ -3518,15 +3527,15 @@
       <c r="G7" s="66"/>
       <c r="H7" s="66"/>
       <c r="I7" s="66"/>
-      <c r="J7" s="75"/>
+      <c r="J7" s="79"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="85" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="66"/>
       <c r="C8" s="67"/>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="78" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="66"/>
@@ -3534,49 +3543,49 @@
       <c r="G8" s="66"/>
       <c r="H8" s="66"/>
       <c r="I8" s="66"/>
-      <c r="J8" s="75"/>
+      <c r="J8" s="79"/>
     </row>
     <row r="9" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="89" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="67"/>
-      <c r="D9" s="89" t="s">
-        <v>76</v>
+      <c r="D9" s="80" t="s">
+        <v>103</v>
       </c>
       <c r="E9" s="66"/>
       <c r="F9" s="66"/>
       <c r="G9" s="66"/>
       <c r="H9" s="66"/>
       <c r="I9" s="66"/>
-      <c r="J9" s="75"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A10" s="83"/>
-      <c r="B10" s="72" t="s">
+      <c r="A10" s="87"/>
+      <c r="B10" s="89" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="67"/>
-      <c r="D10" s="89" t="s">
-        <v>77</v>
+      <c r="D10" s="80" t="s">
+        <v>104</v>
       </c>
       <c r="E10" s="66"/>
       <c r="F10" s="66"/>
       <c r="G10" s="66"/>
       <c r="H10" s="66"/>
       <c r="I10" s="66"/>
-      <c r="J10" s="75"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="84"/>
-      <c r="B11" s="72" t="s">
+      <c r="A11" s="88"/>
+      <c r="B11" s="89" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="67"/>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="78" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="66"/>
@@ -3584,15 +3593,15 @@
       <c r="G11" s="66"/>
       <c r="H11" s="66"/>
       <c r="I11" s="66"/>
-      <c r="J11" s="75"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="73" t="s">
+      <c r="A12" s="85" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="66"/>
       <c r="C12" s="67"/>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="78" t="s">
         <v>71</v>
       </c>
       <c r="E12" s="66"/>
@@ -3600,23 +3609,23 @@
       <c r="G12" s="66"/>
       <c r="H12" s="66"/>
       <c r="I12" s="66"/>
-      <c r="J12" s="75"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="85" t="s">
+      <c r="B13" s="73"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="86"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="74"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4607,6 +4616,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4615,25 +4643,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7488,7 +7497,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="52"/>
@@ -7515,7 +7524,7 @@
       <c r="B2" s="54"/>
       <c r="C2" s="55"/>
       <c r="D2" s="61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E2" s="62"/>
       <c r="F2" s="61" t="s">
@@ -7555,23 +7564,23 @@
       <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="81"/>
+      <c r="B5" s="76"/>
       <c r="C5" s="60"/>
-      <c r="D5" s="94" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="88"/>
+      <c r="D5" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="95" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="66"/>
@@ -7582,19 +7591,19 @@
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
       <c r="I6" s="66"/>
-      <c r="J6" s="75"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="95"/>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1">
       <c r="A8" s="53"/>
@@ -7606,7 +7615,7 @@
       <c r="G8" s="54"/>
       <c r="H8" s="54"/>
       <c r="I8" s="54"/>
-      <c r="J8" s="98"/>
+      <c r="J8" s="100"/>
       <c r="K8" s="40"/>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1">
@@ -7619,7 +7628,7 @@
       <c r="G9" s="54"/>
       <c r="H9" s="54"/>
       <c r="I9" s="54"/>
-      <c r="J9" s="98"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1">
       <c r="A10" s="53"/>
@@ -7631,7 +7640,7 @@
       <c r="G10" s="54"/>
       <c r="H10" s="54"/>
       <c r="I10" s="54"/>
-      <c r="J10" s="98"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1">
       <c r="A11" s="53"/>
@@ -7643,7 +7652,7 @@
       <c r="G11" s="54"/>
       <c r="H11" s="54"/>
       <c r="I11" s="54"/>
-      <c r="J11" s="98"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1">
       <c r="A12" s="53"/>
@@ -7655,7 +7664,7 @@
       <c r="G12" s="54"/>
       <c r="H12" s="54"/>
       <c r="I12" s="54"/>
-      <c r="J12" s="98"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:11" ht="19.5" customHeight="1">
       <c r="A13" s="53"/>
@@ -7667,10 +7676,10 @@
       <c r="G13" s="54"/>
       <c r="H13" s="54"/>
       <c r="I13" s="54"/>
-      <c r="J13" s="98"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="92" t="s">
+      <c r="A14" s="95" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="66"/>
@@ -7681,16 +7690,16 @@
       <c r="G14" s="66"/>
       <c r="H14" s="66"/>
       <c r="I14" s="66"/>
-      <c r="J14" s="75"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="95" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="66"/>
       <c r="C15" s="67"/>
-      <c r="D15" s="74" t="s">
-        <v>104</v>
+      <c r="D15" s="78" t="s">
+        <v>102</v>
       </c>
       <c r="E15" s="66"/>
       <c r="F15" s="66"/>
@@ -7700,11 +7709,11 @@
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="95" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="66"/>
@@ -7721,135 +7730,135 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="99" t="s">
+      <c r="H16" s="101" t="s">
         <v>19</v>
       </c>
       <c r="I16" s="66"/>
-      <c r="J16" s="75"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="93" t="s">
-        <v>83</v>
+      <c r="A17" s="90" t="s">
+        <v>81</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="67"/>
       <c r="D17" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I17" s="41"/>
       <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="93" t="s">
-        <v>84</v>
+      <c r="A18" s="90" t="s">
+        <v>82</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="67"/>
       <c r="D18" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I18" s="41"/>
       <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="93" t="s">
-        <v>85</v>
+      <c r="A19" s="90" t="s">
+        <v>83</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="67"/>
       <c r="D19" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" s="100"/>
-      <c r="J19" s="101"/>
+        <v>86</v>
+      </c>
+      <c r="H19" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="93" t="s">
-        <v>86</v>
+      <c r="A20" s="90" t="s">
+        <v>84</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="67"/>
       <c r="D20" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I20" s="100"/>
-      <c r="J20" s="101"/>
+        <v>94</v>
+      </c>
+      <c r="H20" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="93"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="66"/>
       <c r="C21" s="67"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="101"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="92"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="93"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="66"/>
       <c r="C22" s="67"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="74"/>
+      <c r="H22" s="78"/>
       <c r="I22" s="66"/>
-      <c r="J22" s="75"/>
+      <c r="J22" s="79"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="91"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="82"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="86"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="74"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8830,14 +8839,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8854,11 +8860,14 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8884,7 +8893,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="50" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="52"/>
@@ -8911,7 +8920,7 @@
       <c r="B2" s="54"/>
       <c r="C2" s="55"/>
       <c r="D2" s="61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E2" s="62"/>
       <c r="F2" s="61" t="s">
@@ -8951,23 +8960,23 @@
       <c r="J4" s="48"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="81"/>
+      <c r="B5" s="76"/>
       <c r="C5" s="60"/>
-      <c r="D5" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="88"/>
+      <c r="D5" s="96" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="95" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="66"/>
@@ -8978,19 +8987,19 @@
       <c r="G6" s="66"/>
       <c r="H6" s="66"/>
       <c r="I6" s="66"/>
-      <c r="J6" s="75"/>
+      <c r="J6" s="79"/>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="95"/>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="97"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1">
       <c r="A8" s="53"/>
@@ -9002,7 +9011,7 @@
       <c r="G8" s="54"/>
       <c r="H8" s="54"/>
       <c r="I8" s="54"/>
-      <c r="J8" s="98"/>
+      <c r="J8" s="100"/>
       <c r="K8" s="40"/>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1">
@@ -9015,7 +9024,7 @@
       <c r="G9" s="54"/>
       <c r="H9" s="54"/>
       <c r="I9" s="54"/>
-      <c r="J9" s="98"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1">
       <c r="A10" s="53"/>
@@ -9027,7 +9036,7 @@
       <c r="G10" s="54"/>
       <c r="H10" s="54"/>
       <c r="I10" s="54"/>
-      <c r="J10" s="98"/>
+      <c r="J10" s="100"/>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1">
       <c r="A11" s="53"/>
@@ -9039,7 +9048,7 @@
       <c r="G11" s="54"/>
       <c r="H11" s="54"/>
       <c r="I11" s="54"/>
-      <c r="J11" s="98"/>
+      <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1">
       <c r="A12" s="53"/>
@@ -9051,7 +9060,7 @@
       <c r="G12" s="54"/>
       <c r="H12" s="54"/>
       <c r="I12" s="54"/>
-      <c r="J12" s="98"/>
+      <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:11" ht="19.5" customHeight="1">
       <c r="A13" s="53"/>
@@ -9063,10 +9072,10 @@
       <c r="G13" s="54"/>
       <c r="H13" s="54"/>
       <c r="I13" s="54"/>
-      <c r="J13" s="98"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="92" t="s">
+      <c r="A14" s="95" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="66"/>
@@ -9077,16 +9086,16 @@
       <c r="G14" s="66"/>
       <c r="H14" s="66"/>
       <c r="I14" s="66"/>
-      <c r="J14" s="75"/>
+      <c r="J14" s="79"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="95" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="66"/>
       <c r="C15" s="67"/>
-      <c r="D15" s="74" t="s">
-        <v>103</v>
+      <c r="D15" s="78" t="s">
+        <v>101</v>
       </c>
       <c r="E15" s="66"/>
       <c r="F15" s="66"/>
@@ -9096,11 +9105,11 @@
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="95" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="66"/>
@@ -9117,36 +9126,36 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="99" t="s">
+      <c r="H16" s="101" t="s">
         <v>19</v>
       </c>
       <c r="I16" s="66"/>
-      <c r="J16" s="75"/>
+      <c r="J16" s="79"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="93" t="s">
-        <v>83</v>
+      <c r="A17" s="90" t="s">
+        <v>81</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="67"/>
       <c r="D17" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I17" s="41"/>
       <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="93"/>
+      <c r="A18" s="90"/>
       <c r="B18" s="66"/>
       <c r="C18" s="67"/>
       <c r="D18" s="17"/>
@@ -9158,64 +9167,64 @@
       <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="93"/>
+      <c r="A19" s="90"/>
       <c r="B19" s="66"/>
       <c r="C19" s="67"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="101"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="92"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="93"/>
+      <c r="A20" s="90"/>
       <c r="B20" s="66"/>
       <c r="C20" s="67"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="100"/>
-      <c r="J20" s="101"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="92"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="93"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="66"/>
       <c r="C21" s="67"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="101"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="92"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="93"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="66"/>
       <c r="C22" s="67"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="74"/>
+      <c r="H22" s="78"/>
       <c r="I22" s="66"/>
-      <c r="J22" s="75"/>
+      <c r="J22" s="79"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="91"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="82"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="86"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="74"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10196,6 +10205,21 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="A22:C22"/>
@@ -10210,21 +10234,6 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10244,7 +10253,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="83" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="51"/>
@@ -10255,14 +10264,14 @@
       <c r="G1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
       <c r="J1" s="60"/>
       <c r="K1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
       <c r="N1" s="60"/>
       <c r="O1" s="59" t="s">
         <v>7</v>
@@ -10275,7 +10284,7 @@
       <c r="S1" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="88"/>
+      <c r="T1" s="77"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="53"/>
@@ -10285,19 +10294,19 @@
       <c r="E2" s="54"/>
       <c r="F2" s="55"/>
       <c r="G2" s="61"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
       <c r="J2" s="62"/>
       <c r="K2" s="61"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
       <c r="N2" s="62"/>
       <c r="O2" s="61"/>
       <c r="P2" s="62"/>
       <c r="Q2" s="61"/>
       <c r="R2" s="62"/>
       <c r="S2" s="61"/>
-      <c r="T2" s="97"/>
+      <c r="T2" s="99"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="53"/>
@@ -10319,7 +10328,7 @@
       <c r="Q3" s="63"/>
       <c r="R3" s="55"/>
       <c r="S3" s="63"/>
-      <c r="T3" s="98"/>
+      <c r="T3" s="100"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="56"/>
@@ -10341,36 +10350,36 @@
       <c r="Q4" s="64"/>
       <c r="R4" s="58"/>
       <c r="S4" s="64"/>
-      <c r="T4" s="106"/>
+      <c r="T4" s="110"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
       <c r="F5" s="60"/>
-      <c r="G5" s="87" t="s">
+      <c r="G5" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="88"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="77"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="95" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="66"/>
@@ -10378,7 +10387,7 @@
       <c r="D6" s="66"/>
       <c r="E6" s="66"/>
       <c r="F6" s="67"/>
-      <c r="G6" s="74" t="s">
+      <c r="G6" s="78" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="66"/>
@@ -10393,10 +10402,10 @@
       <c r="Q6" s="66"/>
       <c r="R6" s="66"/>
       <c r="S6" s="66"/>
-      <c r="T6" s="75"/>
+      <c r="T6" s="79"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="95" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="66"/>
@@ -10404,7 +10413,7 @@
       <c r="D7" s="66"/>
       <c r="E7" s="66"/>
       <c r="F7" s="67"/>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="78" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="66"/>
@@ -10419,7 +10428,7 @@
       <c r="Q7" s="66"/>
       <c r="R7" s="66"/>
       <c r="S7" s="66"/>
-      <c r="T7" s="75"/>
+      <c r="T7" s="79"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10618,7 +10627,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="95" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="67"/>
@@ -10626,25 +10635,25 @@
         <v>38</v>
       </c>
       <c r="D15" s="67"/>
-      <c r="E15" s="99" t="s">
+      <c r="E15" s="101" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="67"/>
-      <c r="G15" s="99" t="s">
+      <c r="G15" s="101" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="66"/>
       <c r="I15" s="67"/>
-      <c r="J15" s="99" t="s">
+      <c r="J15" s="101" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="67"/>
-      <c r="L15" s="99" t="s">
+      <c r="L15" s="101" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="66"/>
       <c r="N15" s="67"/>
-      <c r="O15" s="99" t="s">
+      <c r="O15" s="101" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="66"/>
@@ -10660,33 +10669,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="107">
+      <c r="A16" s="102">
         <v>1</v>
       </c>
       <c r="B16" s="67"/>
-      <c r="C16" s="108" t="s">
+      <c r="C16" s="103" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="67"/>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="103" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="67"/>
-      <c r="G16" s="102" t="s">
+      <c r="G16" s="108" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="66"/>
       <c r="I16" s="67"/>
-      <c r="J16" s="102" t="s">
+      <c r="J16" s="108" t="s">
         <v>56</v>
       </c>
       <c r="K16" s="67"/>
-      <c r="L16" s="104" t="s">
+      <c r="L16" s="106" t="s">
         <v>57</v>
       </c>
       <c r="M16" s="66"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="104" t="s">
+      <c r="O16" s="106" t="s">
         <v>58</v>
       </c>
       <c r="P16" s="66"/>
@@ -10702,33 +10711,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="107">
+      <c r="A17" s="102">
         <v>2</v>
       </c>
       <c r="B17" s="67"/>
-      <c r="C17" s="108" t="s">
+      <c r="C17" s="103" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="67"/>
-      <c r="E17" s="108" t="s">
+      <c r="E17" s="103" t="s">
         <v>60</v>
       </c>
       <c r="F17" s="67"/>
-      <c r="G17" s="102" t="s">
+      <c r="G17" s="108" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="66"/>
       <c r="I17" s="67"/>
-      <c r="J17" s="102" t="s">
+      <c r="J17" s="108" t="s">
         <v>62</v>
       </c>
       <c r="K17" s="67"/>
-      <c r="L17" s="104" t="s">
+      <c r="L17" s="106" t="s">
         <v>63</v>
       </c>
       <c r="M17" s="66"/>
       <c r="N17" s="67"/>
-      <c r="O17" s="104" t="s">
+      <c r="O17" s="106" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="66"/>
@@ -10744,21 +10753,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="107"/>
+      <c r="A18" s="102"/>
       <c r="B18" s="67"/>
-      <c r="C18" s="108"/>
+      <c r="C18" s="103"/>
       <c r="D18" s="67"/>
-      <c r="E18" s="108"/>
+      <c r="E18" s="103"/>
       <c r="F18" s="67"/>
-      <c r="G18" s="102"/>
+      <c r="G18" s="108"/>
       <c r="H18" s="66"/>
       <c r="I18" s="67"/>
-      <c r="J18" s="102"/>
+      <c r="J18" s="108"/>
       <c r="K18" s="67"/>
-      <c r="L18" s="104"/>
+      <c r="L18" s="106"/>
       <c r="M18" s="66"/>
       <c r="N18" s="67"/>
-      <c r="O18" s="104"/>
+      <c r="O18" s="106"/>
       <c r="P18" s="66"/>
       <c r="Q18" s="67"/>
       <c r="R18" s="33"/>
@@ -10772,21 +10781,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="107"/>
+      <c r="A19" s="102"/>
       <c r="B19" s="67"/>
-      <c r="C19" s="108"/>
+      <c r="C19" s="103"/>
       <c r="D19" s="67"/>
-      <c r="E19" s="108"/>
+      <c r="E19" s="103"/>
       <c r="F19" s="67"/>
-      <c r="G19" s="102"/>
+      <c r="G19" s="108"/>
       <c r="H19" s="66"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="102"/>
+      <c r="J19" s="108"/>
       <c r="K19" s="67"/>
-      <c r="L19" s="104"/>
+      <c r="L19" s="106"/>
       <c r="M19" s="66"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="104"/>
+      <c r="O19" s="106"/>
       <c r="P19" s="66"/>
       <c r="Q19" s="67"/>
       <c r="R19" s="33"/>
@@ -10800,21 +10809,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="107"/>
+      <c r="A20" s="102"/>
       <c r="B20" s="67"/>
-      <c r="C20" s="108"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="67"/>
-      <c r="E20" s="108"/>
+      <c r="E20" s="103"/>
       <c r="F20" s="67"/>
-      <c r="G20" s="102"/>
+      <c r="G20" s="108"/>
       <c r="H20" s="66"/>
       <c r="I20" s="67"/>
-      <c r="J20" s="102"/>
+      <c r="J20" s="108"/>
       <c r="K20" s="67"/>
-      <c r="L20" s="104"/>
+      <c r="L20" s="106"/>
       <c r="M20" s="66"/>
       <c r="N20" s="67"/>
-      <c r="O20" s="104"/>
+      <c r="O20" s="106"/>
       <c r="P20" s="66"/>
       <c r="Q20" s="67"/>
       <c r="R20" s="33"/>
@@ -10828,21 +10837,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="107"/>
+      <c r="A21" s="102"/>
       <c r="B21" s="67"/>
-      <c r="C21" s="108"/>
+      <c r="C21" s="103"/>
       <c r="D21" s="67"/>
-      <c r="E21" s="108"/>
+      <c r="E21" s="103"/>
       <c r="F21" s="67"/>
-      <c r="G21" s="102"/>
+      <c r="G21" s="108"/>
       <c r="H21" s="66"/>
       <c r="I21" s="67"/>
-      <c r="J21" s="102"/>
+      <c r="J21" s="108"/>
       <c r="K21" s="67"/>
-      <c r="L21" s="104"/>
+      <c r="L21" s="106"/>
       <c r="M21" s="66"/>
       <c r="N21" s="67"/>
-      <c r="O21" s="104"/>
+      <c r="O21" s="106"/>
       <c r="P21" s="66"/>
       <c r="Q21" s="67"/>
       <c r="R21" s="33"/>
@@ -10856,21 +10865,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="107"/>
+      <c r="A22" s="102"/>
       <c r="B22" s="67"/>
-      <c r="C22" s="108"/>
+      <c r="C22" s="103"/>
       <c r="D22" s="67"/>
-      <c r="E22" s="108"/>
+      <c r="E22" s="103"/>
       <c r="F22" s="67"/>
-      <c r="G22" s="102"/>
+      <c r="G22" s="108"/>
       <c r="H22" s="66"/>
       <c r="I22" s="67"/>
-      <c r="J22" s="102"/>
+      <c r="J22" s="108"/>
       <c r="K22" s="67"/>
-      <c r="L22" s="104"/>
+      <c r="L22" s="106"/>
       <c r="M22" s="66"/>
       <c r="N22" s="67"/>
-      <c r="O22" s="104"/>
+      <c r="O22" s="106"/>
       <c r="P22" s="66"/>
       <c r="Q22" s="67"/>
       <c r="R22" s="33"/>
@@ -10884,21 +10893,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="107"/>
+      <c r="A23" s="102"/>
       <c r="B23" s="67"/>
-      <c r="C23" s="108"/>
+      <c r="C23" s="103"/>
       <c r="D23" s="67"/>
-      <c r="E23" s="108"/>
+      <c r="E23" s="103"/>
       <c r="F23" s="67"/>
-      <c r="G23" s="102"/>
+      <c r="G23" s="108"/>
       <c r="H23" s="66"/>
       <c r="I23" s="67"/>
-      <c r="J23" s="102"/>
+      <c r="J23" s="108"/>
       <c r="K23" s="67"/>
-      <c r="L23" s="104"/>
+      <c r="L23" s="106"/>
       <c r="M23" s="66"/>
       <c r="N23" s="67"/>
-      <c r="O23" s="104"/>
+      <c r="O23" s="106"/>
       <c r="P23" s="66"/>
       <c r="Q23" s="67"/>
       <c r="R23" s="33"/>
@@ -10912,21 +10921,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="107"/>
+      <c r="A24" s="102"/>
       <c r="B24" s="67"/>
-      <c r="C24" s="108"/>
+      <c r="C24" s="103"/>
       <c r="D24" s="67"/>
-      <c r="E24" s="108"/>
+      <c r="E24" s="103"/>
       <c r="F24" s="67"/>
-      <c r="G24" s="102"/>
+      <c r="G24" s="108"/>
       <c r="H24" s="66"/>
       <c r="I24" s="67"/>
-      <c r="J24" s="102"/>
+      <c r="J24" s="108"/>
       <c r="K24" s="67"/>
-      <c r="L24" s="104"/>
+      <c r="L24" s="106"/>
       <c r="M24" s="66"/>
       <c r="N24" s="67"/>
-      <c r="O24" s="104"/>
+      <c r="O24" s="106"/>
       <c r="P24" s="66"/>
       <c r="Q24" s="67"/>
       <c r="R24" s="33"/>
@@ -10940,21 +10949,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="107"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="67"/>
-      <c r="C25" s="108"/>
+      <c r="C25" s="103"/>
       <c r="D25" s="67"/>
-      <c r="E25" s="108"/>
+      <c r="E25" s="103"/>
       <c r="F25" s="67"/>
-      <c r="G25" s="102"/>
+      <c r="G25" s="108"/>
       <c r="H25" s="66"/>
       <c r="I25" s="67"/>
-      <c r="J25" s="102"/>
+      <c r="J25" s="108"/>
       <c r="K25" s="67"/>
-      <c r="L25" s="104"/>
+      <c r="L25" s="106"/>
       <c r="M25" s="66"/>
       <c r="N25" s="67"/>
-      <c r="O25" s="104"/>
+      <c r="O25" s="106"/>
       <c r="P25" s="66"/>
       <c r="Q25" s="67"/>
       <c r="R25" s="33"/>
@@ -10968,21 +10977,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="107"/>
+      <c r="A26" s="102"/>
       <c r="B26" s="67"/>
-      <c r="C26" s="108"/>
+      <c r="C26" s="103"/>
       <c r="D26" s="67"/>
-      <c r="E26" s="108"/>
+      <c r="E26" s="103"/>
       <c r="F26" s="67"/>
-      <c r="G26" s="102"/>
+      <c r="G26" s="108"/>
       <c r="H26" s="66"/>
       <c r="I26" s="67"/>
-      <c r="J26" s="102"/>
+      <c r="J26" s="108"/>
       <c r="K26" s="67"/>
-      <c r="L26" s="104"/>
+      <c r="L26" s="106"/>
       <c r="M26" s="66"/>
       <c r="N26" s="67"/>
-      <c r="O26" s="104"/>
+      <c r="O26" s="106"/>
       <c r="P26" s="66"/>
       <c r="Q26" s="67"/>
       <c r="R26" s="33"/>
@@ -10996,21 +11005,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="107"/>
+      <c r="A27" s="102"/>
       <c r="B27" s="67"/>
-      <c r="C27" s="108"/>
+      <c r="C27" s="103"/>
       <c r="D27" s="67"/>
-      <c r="E27" s="108"/>
+      <c r="E27" s="103"/>
       <c r="F27" s="67"/>
-      <c r="G27" s="102"/>
+      <c r="G27" s="108"/>
       <c r="H27" s="66"/>
       <c r="I27" s="67"/>
-      <c r="J27" s="102"/>
+      <c r="J27" s="108"/>
       <c r="K27" s="67"/>
-      <c r="L27" s="104"/>
+      <c r="L27" s="106"/>
       <c r="M27" s="66"/>
       <c r="N27" s="67"/>
-      <c r="O27" s="104"/>
+      <c r="O27" s="106"/>
       <c r="P27" s="66"/>
       <c r="Q27" s="67"/>
       <c r="R27" s="33"/>
@@ -11024,21 +11033,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="107"/>
+      <c r="A28" s="102"/>
       <c r="B28" s="67"/>
-      <c r="C28" s="108"/>
+      <c r="C28" s="103"/>
       <c r="D28" s="67"/>
-      <c r="E28" s="108"/>
+      <c r="E28" s="103"/>
       <c r="F28" s="67"/>
-      <c r="G28" s="102"/>
+      <c r="G28" s="108"/>
       <c r="H28" s="66"/>
       <c r="I28" s="67"/>
-      <c r="J28" s="102"/>
+      <c r="J28" s="108"/>
       <c r="K28" s="67"/>
-      <c r="L28" s="104"/>
+      <c r="L28" s="106"/>
       <c r="M28" s="66"/>
       <c r="N28" s="67"/>
-      <c r="O28" s="104"/>
+      <c r="O28" s="106"/>
       <c r="P28" s="66"/>
       <c r="Q28" s="67"/>
       <c r="R28" s="33"/>
@@ -11052,21 +11061,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="107"/>
+      <c r="A29" s="102"/>
       <c r="B29" s="67"/>
-      <c r="C29" s="108"/>
+      <c r="C29" s="103"/>
       <c r="D29" s="67"/>
-      <c r="E29" s="108"/>
+      <c r="E29" s="103"/>
       <c r="F29" s="67"/>
-      <c r="G29" s="102"/>
+      <c r="G29" s="108"/>
       <c r="H29" s="66"/>
       <c r="I29" s="67"/>
-      <c r="J29" s="102"/>
+      <c r="J29" s="108"/>
       <c r="K29" s="67"/>
-      <c r="L29" s="104"/>
+      <c r="L29" s="106"/>
       <c r="M29" s="66"/>
       <c r="N29" s="67"/>
-      <c r="O29" s="104"/>
+      <c r="O29" s="106"/>
       <c r="P29" s="66"/>
       <c r="Q29" s="67"/>
       <c r="R29" s="33"/>
@@ -11080,21 +11089,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="107"/>
+      <c r="A30" s="102"/>
       <c r="B30" s="67"/>
-      <c r="C30" s="108"/>
+      <c r="C30" s="103"/>
       <c r="D30" s="67"/>
-      <c r="E30" s="108"/>
+      <c r="E30" s="103"/>
       <c r="F30" s="67"/>
-      <c r="G30" s="102"/>
+      <c r="G30" s="108"/>
       <c r="H30" s="66"/>
       <c r="I30" s="67"/>
-      <c r="J30" s="102"/>
+      <c r="J30" s="108"/>
       <c r="K30" s="67"/>
-      <c r="L30" s="104"/>
+      <c r="L30" s="106"/>
       <c r="M30" s="66"/>
       <c r="N30" s="67"/>
-      <c r="O30" s="104"/>
+      <c r="O30" s="106"/>
       <c r="P30" s="66"/>
       <c r="Q30" s="67"/>
       <c r="R30" s="33"/>
@@ -11108,23 +11117,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="110"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="111"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="103"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="77"/>
-      <c r="Q31" s="78"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="82"/>
+      <c r="L31" s="107"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="82"/>
+      <c r="O31" s="107"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="82"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -12122,6 +12131,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -12146,118 +12267,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_ログイン機能.xlsx
+++ b/document/成果物ドキュメント_ログイン機能.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976AAFF4-9B4E-40F7-8F59-F91557380F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074A4176-1381-42E9-862C-776A44F5F8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="画面設計書 (2)" sheetId="8" r:id="rId6"/>
+    <sheet name="画面設計書 (ログイン画面)" sheetId="5" r:id="rId5"/>
+    <sheet name="画面設計書 (ログイン失敗画面)" sheetId="8" r:id="rId6"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="104">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -247,13 +244,6 @@
     <t>62期</t>
     <rPh sb="2" eb="3">
       <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>吉澤昂</t>
-    <rPh sb="0" eb="3">
-      <t>ヨシザワコウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -480,16 +470,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログイン画面失敗</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ログイン画面へ</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -539,6 +519,23 @@
     </rPh>
     <rPh sb="127" eb="129">
       <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン失敗画面</t>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チーム名　62期</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1437,6 +1434,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1458,8 +1479,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1473,44 +1521,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1524,68 +1572,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1594,6 +1582,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1614,17 +1605,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1632,17 +1623,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1663,122 +1660,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>336176</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>840440</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>19611</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="73" name="減算記号 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2B6CC00-3C09-4C47-89B7-7512B4F879F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8051426" y="4752975"/>
-          <a:ext cx="504264" cy="714936"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMinus">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>324971</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>33617</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>829235</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="72" name="減算記号 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{160186B1-6D78-B2E5-AC01-860C801AB895}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8023412" y="3283323"/>
-          <a:ext cx="504264" cy="694765"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMinus">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1847,16 +1728,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>315058</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>287844</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>117230</xdr:rowOff>
+      <xdr:rowOff>62801</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>91829</xdr:colOff>
+      <xdr:colOff>1085151</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>108856</xdr:rowOff>
+      <xdr:rowOff>54427</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1886,7 +1767,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="315058" y="1042516"/>
+          <a:off x="1308380" y="988087"/>
           <a:ext cx="5260450" cy="5216769"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2248,85 +2129,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2346,46 +2227,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
+      <c r="E8" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="65" t="s">
+      <c r="H13" s="59"/>
+      <c r="I13" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="66"/>
-      <c r="K13" s="67"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="59"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="65"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="67"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="59"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="65"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="67"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="59"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2394,13 +2275,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="68" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
+      <c r="G17" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3414,218 +3295,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="59" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="59" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="51">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="55"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="57"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="74" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="43">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="46" t="s">
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="63"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="63"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="63"/>
+    </row>
+    <row r="9" spans="1:10" ht="94.5" customHeight="1">
+      <c r="A9" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="59"/>
+      <c r="D9" s="83" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="63"/>
+    </row>
+    <row r="10" spans="1:10" ht="85.5" customHeight="1">
+      <c r="A10" s="77"/>
+      <c r="B10" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="59"/>
+      <c r="D10" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="63"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="78"/>
+      <c r="B11" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="59"/>
+      <c r="D11" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="48"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="49"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="84" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="75" t="s">
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="63"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="61"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="63"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="78" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="79"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="78" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="79"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="78" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="79"/>
-    </row>
-    <row r="9" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A9" s="86" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="80" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="79"/>
-    </row>
-    <row r="10" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="80" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="79"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="88"/>
-      <c r="B11" s="89" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="79"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="85" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="79"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="72" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="74"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4616,17 +4497,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4635,14 +4513,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4661,72 +4542,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="59" t="s">
+      <c r="A1" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="59" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="43">
+      <c r="G2" s="46"/>
+      <c r="H2" s="51">
         <v>46120</v>
       </c>
-      <c r="I2" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="47"/>
+      <c r="I2" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="48"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="49"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6081,72 +5962,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="59" t="s">
+      <c r="A1" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="59" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="43">
+      <c r="G2" s="46"/>
+      <c r="H2" s="51">
         <v>46121</v>
       </c>
-      <c r="I2" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="47"/>
+      <c r="I2" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="48"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="49"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7496,369 +7377,369 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="44"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="51">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="55"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="56"/>
+    </row>
+    <row r="5" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A5" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="94" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
+    </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1">
+      <c r="A6" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="63"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1">
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
+    </row>
+    <row r="8" spans="1:11" ht="21" customHeight="1">
+      <c r="A8" s="70"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="40"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1">
+      <c r="A9" s="70"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="98"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="98"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="98"/>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="98"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="98"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A14" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="63"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A15" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="61"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A16" s="92" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="61"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="61"/>
+      <c r="J16" s="63"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="93" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>87</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="43">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="48"/>
-    </row>
-    <row r="4" spans="1:11" ht="18" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="48"/>
-    </row>
-    <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="96" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="95" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="79"/>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
-    </row>
-    <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="40"/>
-    </row>
-    <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="100"/>
-    </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="100"/>
-    </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="100"/>
-    </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="100"/>
-    </row>
-    <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="100"/>
-    </row>
-    <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="95" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="79"/>
-    </row>
-    <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="95" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="95" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="101" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="66"/>
-      <c r="J16" s="79"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="90" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>89</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I17" s="41"/>
       <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="90" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="67"/>
+      <c r="A18" s="93" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="61"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="39" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I18" s="41"/>
       <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="93" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="61"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>83</v>
-      </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>85</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="78" t="s">
-        <v>96</v>
-      </c>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
+        <v>84</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="100"/>
+      <c r="J19" s="101"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="66"/>
-      <c r="C20" s="67"/>
+      <c r="A20" s="93" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="61"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="I20" s="91"/>
-      <c r="J20" s="92"/>
+        <v>92</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="100"/>
+      <c r="J20" s="101"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
+      <c r="A21" s="93"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="92"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="101"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="67"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="79"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="63"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="94"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="82"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="74"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8839,11 +8720,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8860,14 +8744,11 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8892,272 +8773,272 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="59" t="s">
+      <c r="A1" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="59" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="61" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="51">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="55"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="56"/>
+    </row>
+    <row r="5" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A5" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
+    </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1">
+      <c r="A6" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="63"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1">
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
+    </row>
+    <row r="8" spans="1:11" ht="21" customHeight="1">
+      <c r="A8" s="70"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="40"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1">
+      <c r="A9" s="70"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="98"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="98"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="98"/>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="98"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="98"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A14" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="63"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A15" s="92" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="61"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="43">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="48"/>
-    </row>
-    <row r="4" spans="1:11" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="48"/>
-    </row>
-    <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="96" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="77"/>
-    </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="95" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="79"/>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
-    </row>
-    <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="40"/>
-    </row>
-    <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="100"/>
-    </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="100"/>
-    </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="100"/>
-    </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="100"/>
-    </row>
-    <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="100"/>
-    </row>
-    <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="95" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="79"/>
-    </row>
-    <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="95" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="78" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A16" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="95" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="101" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="66"/>
-      <c r="J16" s="79"/>
+      <c r="H16" s="99" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="61"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="90" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
+      <c r="A17" s="93" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="61"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I17" s="41"/>
       <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="90"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="67"/>
+      <c r="A18" s="93"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
@@ -9167,64 +9048,64 @@
       <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
+      <c r="A19" s="93"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="101"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="67"/>
+      <c r="A20" s="93"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="92"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="101"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
+      <c r="A21" s="93"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="92"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="101"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="67"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="59"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="79"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="63"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="94"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="82"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="74"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10205,6 +10086,20 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
@@ -10220,20 +10115,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10253,182 +10134,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="44"/>
+      <c r="S1" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="82"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="97"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="98"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="106"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="59" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="60"/>
-      <c r="S1" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="77"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="99"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="100"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="110"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="75" t="s">
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="82"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="76"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="76"/>
-      <c r="Q5" s="76"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="76"/>
-      <c r="T5" s="77"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="95" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="63"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="66"/>
-      <c r="P6" s="66"/>
-      <c r="Q6" s="66"/>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="79"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="95" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="66"/>
-      <c r="M7" s="66"/>
-      <c r="N7" s="66"/>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66"/>
-      <c r="T7" s="79"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="63"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10456,11 +10337,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -10490,7 +10371,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -10520,7 +10401,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -10550,7 +10431,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -10580,7 +10461,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -10627,79 +10508,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="59"/>
+      <c r="C15" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="59"/>
+      <c r="E15" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="109" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="101" t="s">
+      <c r="F15" s="59"/>
+      <c r="G15" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="67"/>
-      <c r="G15" s="101" t="s">
+      <c r="H15" s="61"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="66"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="101" t="s">
+      <c r="K15" s="59"/>
+      <c r="L15" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="67"/>
-      <c r="L15" s="101" t="s">
+      <c r="M15" s="61"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="66"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="101" t="s">
+      <c r="P15" s="61"/>
+      <c r="Q15" s="59"/>
+      <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="67"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="107">
+        <v>1</v>
+      </c>
+      <c r="B16" s="59"/>
+      <c r="C16" s="108" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="102">
-        <v>1</v>
-      </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="103" t="s">
+      <c r="D16" s="59"/>
+      <c r="E16" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="103" t="s">
+      <c r="F16" s="59"/>
+      <c r="G16" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="67"/>
-      <c r="G16" s="108" t="s">
+      <c r="H16" s="61"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="66"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="108" t="s">
+      <c r="K16" s="59"/>
+      <c r="L16" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="67"/>
-      <c r="L16" s="106" t="s">
+      <c r="M16" s="61"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="66"/>
-      <c r="N16" s="67"/>
-      <c r="O16" s="106" t="s">
-        <v>58</v>
-      </c>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="67"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="59"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -10711,37 +10592,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="102">
+      <c r="A17" s="107">
         <v>2</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="103" t="s">
+      <c r="B17" s="59"/>
+      <c r="C17" s="108" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="59"/>
+      <c r="E17" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="103" t="s">
+      <c r="F17" s="59"/>
+      <c r="G17" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="108" t="s">
+      <c r="H17" s="61"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="66"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="108" t="s">
+      <c r="K17" s="59"/>
+      <c r="L17" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="67"/>
-      <c r="L17" s="106" t="s">
+      <c r="M17" s="61"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="66"/>
-      <c r="N17" s="67"/>
-      <c r="O17" s="106" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="67"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="59"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -10753,23 +10634,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="106"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="67"/>
+      <c r="A18" s="107"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="59"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -10781,23 +10662,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="67"/>
+      <c r="A19" s="107"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="59"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -10809,23 +10690,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="67"/>
+      <c r="A20" s="107"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="59"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="59"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="59"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -10837,23 +10718,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="67"/>
+      <c r="A21" s="107"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="104"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="59"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -10865,23 +10746,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="67"/>
+      <c r="A22" s="107"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="104"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="59"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -10893,23 +10774,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="67"/>
+      <c r="A23" s="107"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="59"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -10921,23 +10802,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="67"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="67"/>
-      <c r="O24" s="106"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="67"/>
+      <c r="A24" s="107"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="59"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -10949,23 +10830,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="67"/>
+      <c r="A25" s="107"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="59"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -10977,23 +10858,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="67"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="67"/>
+      <c r="A26" s="107"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="59"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -11005,23 +10886,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="67"/>
+      <c r="A27" s="107"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="59"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -11033,23 +10914,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="67"/>
+      <c r="A28" s="107"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="59"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -11061,23 +10942,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="67"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="106"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="67"/>
+      <c r="A29" s="107"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="104"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="59"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -11089,23 +10970,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="106"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="67"/>
+      <c r="A30" s="107"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="59"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -11117,23 +10998,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="104"/>
-      <c r="B31" s="82"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="82"/>
-      <c r="O31" s="107"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="82"/>
+      <c r="A31" s="110"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="103"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="65"/>
+      <c r="Q31" s="66"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -12131,62 +12012,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12211,62 +12092,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_ログイン機能.xlsx
+++ b/document/成果物ドキュメント_ログイン機能.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER123\Desktop\作業中\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFEDE69-6B50-4A39-AEA7-5F76CEA63FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A860ED-1301-45DF-9BA1-F49C049AE049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="2" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="画面設計書 (ログイン画面)" sheetId="5" r:id="rId5"/>
+    <sheet name="画面設計書 (ログイン失敗画面)" sheetId="8" r:id="rId6"/>
+    <sheet name="画面設計書 (メニュー画面)" sheetId="9" r:id="rId7"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,18 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="109">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -250,84 +246,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>吉澤昂</t>
-    <rPh sb="0" eb="3">
-      <t>ヨシザワコウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ログイン機能</t>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ユーザー情報を認証し問題なければメニュー画面へ遷移する</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニンショウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>セキュリティ観点からエラー内容の詳細を伝えない</t>
-    <rPh sb="6" eb="8">
-      <t>カンテン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ツタ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ログインが完了しシステムが使用できるようになる</t>
-    <rPh sb="5" eb="7">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>吉澤</t>
     <rPh sb="0" eb="2">
       <t>ヨシザワ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>未ログイン状態であること、DBにユーザー情報が登録されていること</t>
-    <rPh sb="0" eb="1">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -342,25 +263,6 @@
     </rPh>
     <rPh sb="6" eb="9">
       <t>ジュウギョウイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.ユーザーがログイン画面を開く
-2.ユーザーがユーザIDとパスワードを入力する
-3.ユーザーが「ログイン」ボタンを押下する
-4.システムがユーザーIDとパスワードを認証に成功する
-5.システムがメニュー画面を表示する</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>4a.ユーザーが入力したユーザーIDとパスワードの片方、または両方が間違っていた場合
-4a1.システムがユーザーIDとパスワードの認証に失敗する
-4a2.システムが認証失敗画面にて「ログインに失敗しました。」と表示する
-4a3.ユーザーが「ログイン画面へ」ボタンを押下する
-4a4.基本フロー1.へ</t>
-    <rPh sb="96" eb="98">
-      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -419,32 +321,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>login-servlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>パスワード入力</t>
-    <rPh sb="5" eb="7">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>userId</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ユーザーID入力</t>
-    <rPh sb="6" eb="8">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>フォーム送信ボタン</t>
-    <rPh sb="4" eb="6">
-      <t>ソウシン</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -452,53 +329,201 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>取消ボタン</t>
-    <rPh sb="0" eb="2">
-      <t>トリケシ</t>
+    <t>TaskManager62システム</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン画面へ</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>取消</t>
-    <rPh sb="0" eb="2">
-      <t>トリケシ</t>
+    <t>login.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン失敗画面</t>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>入力したユーザーIDとパスワードを取り消す</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ケ</t>
+    <t>チーム名　62期</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>入力した情報を次の画面へ送信する</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ソウシン</t>
+    <t>ログインする</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1．ユーザーがログイン画面でユーザーIDとパスワードを入力する
+2．ユーザーがログインを選択する
+3．システムがメニュー画面を表示する</t>
+    <rPh sb="44" eb="46">
+      <t>センタク</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>TaskManager62システム</t>
+    <t>3a． ユーザーが入力したユーザーIDとパスワードの片方、または両方が間違っていた場合
+3a1．システムがユーザーIDとパスワードの認証に失敗し、ログイン失敗画面を表示する
+3a2．ユーザーがログイン画面に戻る
+3a3．システムがログイン画面を表示する
+3a4．基本フロー1.へ</t>
+    <rPh sb="77" eb="81">
+      <t>シッパイガメン</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザーがシステムにログインしていないこと、データベースにユーザーの情報が登録されていること</t>
+    <rPh sb="34" eb="36">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>セキュリティの観点からエラー内容の詳細を表示しない</t>
+    <rPh sb="7" eb="9">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザーのログインが完了し、システムが使用できるようになること</t>
+    <rPh sb="10" eb="12">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>パスワード</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザーID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システムがユーザーを認証し、ユーザーがシステムにログインする</t>
+    <rPh sb="10" eb="12">
+      <t>ニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力必須、最大24文字</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクヒッス</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力必須、最大32文字</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクヒッス</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>GET</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>クリア</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>login-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-register-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-list-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>logout.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク一覧</t>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1384,11 +1409,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1396,20 +1421,116 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1420,29 +1541,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1450,23 +1553,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1479,9 +1567,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1498,80 +1583,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1603,6 +1622,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1622,141 +1647,25 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>336176</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>205555</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>117010</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>840440</xdr:colOff>
+      <xdr:colOff>227108</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>19611</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="73" name="減算記号 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2B6CC00-3C09-4C47-89B7-7512B4F879F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8051426" y="4752975"/>
-          <a:ext cx="504264" cy="714936"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMinus">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>324971</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>33617</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>829235</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>100853</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="72" name="減算記号 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{160186B1-6D78-B2E5-AC01-860C801AB895}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8023412" y="3283323"/>
-          <a:ext cx="504264" cy="694765"/>
-        </a:xfrm>
-        <a:prstGeom prst="mathMinus">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent6"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent6"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>138545</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A882EA0-F2BE-C1CF-CB1B-4B2A77FE2BC0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93BF632B-26F6-DD72-CFBE-7BA91104D988}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1779,8 +1688,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="114300" y="1019175"/>
-          <a:ext cx="8096250" cy="1905000"/>
+          <a:off x="205555" y="1017555"/>
+          <a:ext cx="7710826" cy="4385717"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1806,23 +1715,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>605117</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>67236</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>68036</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>108858</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>78440</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>95302</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>740391</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98DD2781-2B5B-9B4E-02C2-43DB890DF75C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9481126A-5723-2DCD-7347-D276FDE2E335}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1845,8 +1754,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1647264" y="963707"/>
-          <a:ext cx="5020235" cy="4420771"/>
+          <a:off x="408215" y="1197429"/>
+          <a:ext cx="8047426" cy="3782785"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1873,22 +1782,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>266699</xdr:rowOff>
+      <xdr:colOff>257735</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>540544</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>28574</xdr:rowOff>
+      <xdr:colOff>918882</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>242241</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00C493BB-4EC7-3D87-63E1-04ECE857B887}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E2D78E6-E6AA-33E0-7B01-9BD09C690C72}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1911,8 +1820,140 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2762250" y="1543049"/>
-          <a:ext cx="3283744" cy="1876425"/>
+          <a:off x="2431676" y="1546411"/>
+          <a:ext cx="3989294" cy="1833477"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>425824</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>482837</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>116700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30D1AE4B-A98C-2105-5DB5-E5DB997A2D1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2599765" y="1680882"/>
+          <a:ext cx="3385160" cy="1573465"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1030940</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>112057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>145676</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>155117</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA40796B-FFCF-8B1D-31F4-A91B5EBD3639}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3204881" y="1636057"/>
+          <a:ext cx="2442883" cy="1656707"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2141,85 +2182,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2239,46 +2280,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="E8" s="82" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="43" t="s">
+      <c r="G13" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="83">
+        <v>46127</v>
+      </c>
+      <c r="J13" s="43"/>
+      <c r="K13" s="46"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="43"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="46"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="43"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="45"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="46"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2287,13 +2328,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
+      <c r="G17" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3307,218 +3348,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="87" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="83" t="s">
+      <c r="G1" s="55"/>
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="83" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="73">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="84" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="92" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="84" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="84" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="92" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="44"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="92" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="44"/>
+    </row>
+    <row r="9" spans="1:10" ht="94.5" customHeight="1">
+      <c r="A9" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="44"/>
+    </row>
+    <row r="10" spans="1:10" ht="85.5" customHeight="1">
+      <c r="A10" s="94"/>
+      <c r="B10" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="88">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="77" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="80"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="81"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="82"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="56"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="72" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="58"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="72" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A9" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="76" t="s">
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="44"/>
+    </row>
+    <row r="11" spans="1:10" ht="78.75" customHeight="1">
+      <c r="A11" s="95"/>
+      <c r="B11" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="59" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="76" t="s">
+      <c r="C11" s="46"/>
+      <c r="D11" s="85" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="44"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="75"/>
-      <c r="B11" s="76" t="s">
+      <c r="B12" s="43"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="44"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="53"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="71" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4554,72 +4595,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="83" t="s">
+      <c r="A1" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="55"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="83" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="84" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="73">
+        <v>46120</v>
+      </c>
+      <c r="I2" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="88">
-        <v>46120</v>
-      </c>
-      <c r="I2" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="80"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="81"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="82"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -4791,7 +4832,6 @@
     <row r="19" spans="1:11" ht="12.75" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
@@ -5974,72 +6014,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="83" t="s">
+      <c r="A1" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="55"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="83" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="84" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="73">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="88">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="80"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="81"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="82"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6080,7 +6120,6 @@
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -6153,7 +6192,6 @@
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
@@ -6165,7 +6203,6 @@
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -6177,7 +6214,6 @@
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
@@ -6193,7 +6229,6 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
@@ -7380,7 +7415,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:K997"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="5.140625" customWidth="1"/>
@@ -7391,370 +7426,333 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="83" t="s">
+      <c r="A1" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="55"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="83" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="88">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="73">
         <v>46121</v>
       </c>
-      <c r="I2" s="77" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="80"/>
+      <c r="I2" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="81"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="81"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1">
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+    </row>
+    <row r="8" spans="1:11" ht="21" customHeight="1">
+      <c r="A8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="39"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1">
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="66"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1">
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="66"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="66"/>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="66"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="66"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A14" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="96" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="56"/>
-    </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="95" t="s">
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A15" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="58"/>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
-    </row>
-    <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="40"/>
-    </row>
-    <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="65"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="100"/>
-    </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="65"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="100"/>
-    </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="100"/>
-    </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="100"/>
-    </row>
-    <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="100"/>
-    </row>
-    <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="95" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="95" t="s">
+      <c r="J15" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A16" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="15" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="E16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="95" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="101" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="58"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="90" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>92</v>
-      </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="39" t="s">
-        <v>93</v>
+      <c r="H17" s="40" t="s">
+        <v>97</v>
       </c>
       <c r="I17" s="41"/>
       <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="44"/>
-      <c r="C18" s="45"/>
+      <c r="A18" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="46"/>
       <c r="D18" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="39" t="s">
-        <v>91</v>
+      <c r="H18" s="40" t="s">
+        <v>98</v>
       </c>
       <c r="I18" s="41"/>
       <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="90" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="43"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="17" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="I19" s="91"/>
-      <c r="J19" s="92"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="I20" s="91"/>
-      <c r="J20" s="92"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="92"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="58"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="94"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53"/>
-    </row>
+        <v>78</v>
+      </c>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="42"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A20" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="58"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="71"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="72"/>
+    </row>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8729,11 +8727,9 @@
     <row r="995" ht="12.75" customHeight="1"/>
     <row r="996" ht="12.75" customHeight="1"/>
     <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="25">
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
@@ -8742,7 +8738,7 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
@@ -8753,16 +8749,11 @@
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H19:J19"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8772,6 +8763,2732 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6BFCDD-09C4-4E48-84F5-F0B516991230}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K994"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="5.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="55"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="73">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A5" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1">
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+    </row>
+    <row r="8" spans="1:11" ht="21" customHeight="1">
+      <c r="A8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="39"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1">
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="66"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1">
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="66"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="66"/>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="66"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="66"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A14" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A15" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A16" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="111"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC994C6-8959-4306-B773-73B46E94705D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K994"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="2" width="5.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="55"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="69"/>
+      <c r="F2" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="73">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A5" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="62"/>
+    </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1">
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="65"/>
+    </row>
+    <row r="8" spans="1:11" ht="21" customHeight="1">
+      <c r="A8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="39"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1">
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="66"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1">
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="66"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1">
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="66"/>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="66"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="66"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A14" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A15" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A16" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="111"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="44"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="43"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="43"/>
+      <c r="J20" s="44"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A21" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="71"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="111"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="44"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="43"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="43"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="43"/>
+      <c r="J24" s="44"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A25" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="58"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="71"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="111"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:H23"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -8782,182 +11499,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="87" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="55"/>
+      <c r="S1" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="62"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="66"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="108"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="83" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="83" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="83" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="83" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="71"/>
-      <c r="S1" s="83" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="56"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="84"/>
-      <c r="T2" s="99"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="100"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="87"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="87"/>
-      <c r="T4" s="110"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="62"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="54" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="44"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="56"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="95" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="58"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="95" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="58"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="44"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8985,11 +11702,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -9019,7 +11736,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -9049,7 +11766,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -9079,7 +11796,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -9109,7 +11826,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -9156,79 +11873,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="46"/>
+      <c r="C15" s="107" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="46"/>
+      <c r="E15" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="46"/>
+      <c r="G15" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="109" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="101" t="s">
+      <c r="H15" s="43"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="101" t="s">
+      <c r="K15" s="46"/>
+      <c r="L15" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="101" t="s">
+      <c r="M15" s="43"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="101" t="s">
+      <c r="P15" s="43"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="101" t="s">
+      <c r="S15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="100">
+        <v>1</v>
+      </c>
+      <c r="B16" s="46"/>
+      <c r="C16" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="32" t="s">
+      <c r="D16" s="46"/>
+      <c r="E16" s="101" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="102">
-        <v>1</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="103" t="s">
+      <c r="F16" s="46"/>
+      <c r="G16" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="103" t="s">
+      <c r="H16" s="43"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="108" t="s">
+      <c r="K16" s="46"/>
+      <c r="L16" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="108" t="s">
+      <c r="M16" s="43"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="45"/>
-      <c r="L16" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16" s="44"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="106" t="s">
-        <v>58</v>
-      </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="45"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="46"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -9240,37 +11957,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="102">
+      <c r="A17" s="100">
         <v>2</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="103" t="s">
+      <c r="B17" s="46"/>
+      <c r="C17" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="46"/>
+      <c r="E17" s="101" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="46"/>
+      <c r="G17" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="103" t="s">
+      <c r="H17" s="43"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="108" t="s">
+      <c r="K17" s="46"/>
+      <c r="L17" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="108" t="s">
+      <c r="M17" s="43"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="45"/>
-      <c r="L17" s="106" t="s">
-        <v>63</v>
-      </c>
-      <c r="M17" s="44"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="106" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="45"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="46"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -9282,23 +11999,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="106"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="45"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="46"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -9310,23 +12027,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="45"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="46"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -9338,23 +12055,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="106"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="45"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="46"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -9366,23 +12083,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="45"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="104"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="104"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="46"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -9394,23 +12111,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="106"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="45"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="106"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="104"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="46"/>
+      <c r="O22" s="104"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="46"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -9422,23 +12139,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="45"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="46"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="43"/>
+      <c r="Q23" s="46"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -9450,23 +12167,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="106"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="45"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="43"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="43"/>
+      <c r="Q24" s="46"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -9478,23 +12195,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="45"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="104"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="104"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="46"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -9506,23 +12223,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="108"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="45"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="104"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="46"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -9534,23 +12251,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="45"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="43"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="46"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -9562,23 +12279,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="108"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="101"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="106"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="46"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -9590,23 +12307,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="108"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="108"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="106"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="45"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="101"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="106"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="43"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="104"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="46"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -9618,23 +12335,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="108"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="108"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="106"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="45"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="101"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="46"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -9646,23 +12363,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="104"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="107"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="107"/>
-      <c r="P31" s="52"/>
-      <c r="Q31" s="61"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="59"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>

--- a/document/成果物ドキュメント_ログイン機能.xlsx
+++ b/document/成果物ドキュメント_ログイン機能.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER123\Desktop\作業中\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A860ED-1301-45DF-9BA1-F49C049AE049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D03F8DA-62E7-4F8C-ACE7-CE79DE9D6F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="45" windowWidth="15135" windowHeight="7665" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -397,16 +397,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザーがシステムにログインしていないこと、データベースにユーザーの情報が登録されていること</t>
-    <rPh sb="34" eb="36">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>セキュリティの観点からエラー内容の詳細を表示しない</t>
     <rPh sb="7" eb="9">
       <t>カンテン</t>
@@ -524,6 +514,17 @@
   </si>
   <si>
     <t>ログアウト</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザーがシステムにログインしていないこと
+データベースにユーザーの情報が登録されていること</t>
+    <rPh sb="34" eb="36">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>トウロク</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1412,29 +1413,80 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1448,61 +1500,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1511,20 +1527,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1544,52 +1554,64 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1598,35 +1620,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2182,85 +2183,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2280,46 +2281,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="82" t="s">
+      <c r="E8" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="78" t="s">
+      <c r="G13" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="83">
+      <c r="H13" s="56"/>
+      <c r="I13" s="86">
         <v>46127</v>
       </c>
-      <c r="J13" s="43"/>
-      <c r="K13" s="46"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="56"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="78"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="46"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="56"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="78"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="46"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="56"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2328,13 +2329,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="79" t="s">
+      <c r="G17" s="82" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3348,19 +3349,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3372,194 +3373,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="73">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
         <v>46121</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="84" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="62"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="40" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="44"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="92" t="s">
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="60"/>
+    </row>
+    <row r="8" spans="1:10" ht="32.25" customHeight="1">
+      <c r="A8" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="40" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="60"/>
+    </row>
+    <row r="9" spans="1:10" ht="94.5" customHeight="1">
+      <c r="A9" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="60"/>
+    </row>
+    <row r="10" spans="1:10" ht="85.5" customHeight="1">
+      <c r="A10" s="74"/>
+      <c r="B10" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="60"/>
+    </row>
+    <row r="11" spans="1:10" ht="78.75" customHeight="1">
+      <c r="A11" s="75"/>
+      <c r="B11" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="60"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="60"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="44"/>
-    </row>
-    <row r="9" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A9" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="96" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="85" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
-    </row>
-    <row r="10" spans="1:10" ht="85.5" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="96" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="85" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="44"/>
-    </row>
-    <row r="11" spans="1:10" ht="78.75" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="85" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="44"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="92" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="44"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="86" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="72"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4550,17 +4551,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4569,14 +4567,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4595,19 +4596,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4619,48 +4620,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="73">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
         <v>46120</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6014,19 +6015,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -6038,48 +6039,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="73">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
         <v>46121</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7426,19 +7427,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7450,191 +7451,191 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="73">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
         <v>46121</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="61" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="62"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="66"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="98"/>
       <c r="K8" s="39"/>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="66"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="66"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="66"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="66"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="66"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="44"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="60"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="46"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="59" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -7643,11 +7644,11 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="46"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -7660,20 +7661,20 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="44"/>
+      <c r="H16" s="99" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="58"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="46"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="56"/>
       <c r="D17" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>71</v>
@@ -7682,20 +7683,20 @@
         <v>80</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="41"/>
-      <c r="J17" s="42"/>
+      <c r="H17" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="88"/>
+      <c r="J17" s="89"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="46"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>71</v>
@@ -7704,18 +7705,18 @@
         <v>72</v>
       </c>
       <c r="G18" s="18"/>
-      <c r="H18" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" s="41"/>
-      <c r="J18" s="42"/>
+      <c r="H18" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="88"/>
+      <c r="J18" s="89"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="46"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="17" t="s">
         <v>78</v>
       </c>
@@ -7726,29 +7727,29 @@
       <c r="G19" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="40"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="42"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="59"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63"/>
       <c r="D20" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>81</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="71"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="72"/>
+        <v>99</v>
+      </c>
+      <c r="H20" s="76"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="77"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8729,11 +8730,10 @@
     <row r="997" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
@@ -8750,10 +8750,11 @@
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8778,19 +8779,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8802,204 +8803,204 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="73">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
         <v>46121</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="61" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="94" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="62"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="66"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="98"/>
       <c r="K8" s="39"/>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="66"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="98"/>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="66"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="98"/>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="66"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="98"/>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="66"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="98"/>
     </row>
     <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="66"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="98"/>
     </row>
     <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="44"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="60"/>
     </row>
     <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="40" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="46"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="46"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -9012,18 +9013,18 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="67" t="s">
+      <c r="H16" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="44"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="19" t="s">
         <v>83</v>
       </c>
@@ -9034,9 +9035,9 @@
       <c r="G17" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="111"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="101"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10017,6 +10018,10 @@
     <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
@@ -10032,10 +10037,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10060,19 +10061,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10084,191 +10085,191 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="68" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="69"/>
-      <c r="F2" s="68" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="69"/>
-      <c r="H2" s="73">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
         <v>46121</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:11" ht="28.5" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="61" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
+    </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1">
+      <c r="A6" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1">
+      <c r="A7" s="95"/>
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
+    </row>
+    <row r="8" spans="1:11" ht="21" customHeight="1">
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="39"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1">
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="98"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1">
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="98"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1">
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="98"/>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1">
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="98"/>
+    </row>
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="98"/>
+    </row>
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A14" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="60"/>
+    </row>
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A15" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="59" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="62"/>
-    </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
-    </row>
-    <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="39"/>
-    </row>
-    <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="66"/>
-    </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="66"/>
-    </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="66"/>
-    </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="66"/>
-    </row>
-    <row r="13" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="66"/>
-    </row>
-    <row r="14" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A14" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="44"/>
-    </row>
-    <row r="15" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A15" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="46"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>24</v>
       </c>
@@ -10277,11 +10278,11 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="46"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>26</v>
       </c>
@@ -10294,59 +10295,59 @@
       <c r="G16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="67" t="s">
+      <c r="H16" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="44"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>77</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="76"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="101"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="60"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="58"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="111"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="44"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="46"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="56"/>
       <c r="I19" s="15" t="s">
         <v>24</v>
       </c>
@@ -10355,11 +10356,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="46"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="15" t="s">
         <v>26</v>
       </c>
@@ -10372,72 +10373,72 @@
       <c r="G20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="67" t="s">
+      <c r="H20" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="44"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="60"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="59"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
       <c r="D21" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>77</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" s="71"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="111"/>
+        <v>106</v>
+      </c>
+      <c r="H21" s="76"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="101"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="44"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="60"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="46"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="56"/>
       <c r="I23" s="15" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="46"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="15" t="s">
         <v>26</v>
       </c>
@@ -10450,31 +10451,31 @@
       <c r="G24" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H24" s="67" t="s">
+      <c r="H24" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="43"/>
-      <c r="J24" s="44"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="60"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="59"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="63"/>
       <c r="D25" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>77</v>
       </c>
       <c r="F25" s="20"/>
       <c r="G25" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25" s="71"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="111"/>
+        <v>107</v>
+      </c>
+      <c r="H25" s="76"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="101"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11447,6 +11448,23 @@
     <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A25:C25"/>
@@ -11463,23 +11481,6 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:H23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11499,182 +11500,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="56" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="56" t="s">
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="56" t="s">
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="56" t="s">
+      <c r="P1" s="41"/>
+      <c r="Q1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="55"/>
-      <c r="S1" s="56" t="s">
+      <c r="R1" s="41"/>
+      <c r="S1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="62"/>
+      <c r="T1" s="79"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="68"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="68"/>
-      <c r="T2" s="65"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="97"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="66"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="98"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="90"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="90"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="108"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="106"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="84" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="62"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="79"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="40" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="44"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="60"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="40" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="44"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="58"/>
+      <c r="Q7" s="58"/>
+      <c r="R7" s="58"/>
+      <c r="S7" s="58"/>
+      <c r="T7" s="60"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11873,37 +11874,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="107" t="s">
+      <c r="B15" s="56"/>
+      <c r="C15" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="46"/>
-      <c r="E15" s="67" t="s">
+      <c r="D15" s="56"/>
+      <c r="E15" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="67" t="s">
+      <c r="F15" s="56"/>
+      <c r="G15" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="67" t="s">
+      <c r="H15" s="58"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="46"/>
-      <c r="L15" s="67" t="s">
+      <c r="K15" s="56"/>
+      <c r="L15" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="43"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="67" t="s">
+      <c r="M15" s="58"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="46"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="56"/>
       <c r="R15" s="15" t="s">
         <v>48</v>
       </c>
@@ -11915,37 +11916,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="100">
+      <c r="A16" s="107">
         <v>1</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="101" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="46"/>
-      <c r="E16" s="101" t="s">
+      <c r="D16" s="56"/>
+      <c r="E16" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="106" t="s">
+      <c r="F16" s="56"/>
+      <c r="G16" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="106" t="s">
+      <c r="H16" s="58"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="46"/>
+      <c r="K16" s="56"/>
       <c r="L16" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="43"/>
-      <c r="N16" s="46"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="56"/>
       <c r="O16" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="46"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="56"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -11957,37 +11958,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="107">
         <v>2</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="101" t="s">
+      <c r="B17" s="56"/>
+      <c r="C17" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="101" t="s">
+      <c r="D17" s="56"/>
+      <c r="E17" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="46"/>
-      <c r="G17" s="106" t="s">
+      <c r="F17" s="56"/>
+      <c r="G17" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="106" t="s">
+      <c r="H17" s="58"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="46"/>
+      <c r="K17" s="56"/>
       <c r="L17" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="43"/>
-      <c r="N17" s="46"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="56"/>
       <c r="O17" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="46"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="56"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -11999,23 +12000,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="46"/>
+      <c r="A18" s="107"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="56"/>
       <c r="L18" s="104"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="46"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="56"/>
       <c r="O18" s="104"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="46"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="56"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12027,23 +12028,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="46"/>
+      <c r="A19" s="107"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="102"/>
+      <c r="K19" s="56"/>
       <c r="L19" s="104"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="46"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="56"/>
       <c r="O19" s="104"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="46"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="56"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12055,23 +12056,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="46"/>
+      <c r="A20" s="107"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="56"/>
       <c r="L20" s="104"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="46"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="56"/>
       <c r="O20" s="104"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="46"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="56"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12083,23 +12084,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="46"/>
+      <c r="A21" s="107"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="102"/>
+      <c r="K21" s="56"/>
       <c r="L21" s="104"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="46"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="56"/>
       <c r="O21" s="104"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="46"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="56"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12111,23 +12112,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="46"/>
+      <c r="A22" s="107"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="102"/>
+      <c r="K22" s="56"/>
       <c r="L22" s="104"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="46"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="56"/>
       <c r="O22" s="104"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="46"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="56"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12139,23 +12140,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="100"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="46"/>
+      <c r="A23" s="107"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="108"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="56"/>
       <c r="L23" s="104"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="46"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="56"/>
       <c r="O23" s="104"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="46"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="56"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12167,23 +12168,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="100"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="46"/>
+      <c r="A24" s="107"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="56"/>
       <c r="L24" s="104"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="46"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="56"/>
       <c r="O24" s="104"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="46"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="56"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12195,23 +12196,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="46"/>
+      <c r="A25" s="107"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="56"/>
       <c r="L25" s="104"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="46"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="56"/>
       <c r="O25" s="104"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="46"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="56"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12223,23 +12224,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="100"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="46"/>
+      <c r="A26" s="107"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="56"/>
       <c r="L26" s="104"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="46"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="56"/>
       <c r="O26" s="104"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="46"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="56"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12251,23 +12252,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="46"/>
+      <c r="A27" s="107"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="102"/>
+      <c r="K27" s="56"/>
       <c r="L27" s="104"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="46"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="56"/>
       <c r="O27" s="104"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="46"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="56"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12279,23 +12280,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="100"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="46"/>
+      <c r="A28" s="107"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="108"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="56"/>
       <c r="L28" s="104"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="46"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="56"/>
       <c r="O28" s="104"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="46"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="56"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12307,23 +12308,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="46"/>
+      <c r="A29" s="107"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="108"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="56"/>
       <c r="L29" s="104"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="46"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="56"/>
       <c r="O29" s="104"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="46"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="56"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12335,23 +12336,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="46"/>
+      <c r="A30" s="107"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="108"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="56"/>
       <c r="L30" s="104"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="46"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="56"/>
       <c r="O30" s="104"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="46"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="56"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12363,23 +12364,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="59"/>
+      <c r="A31" s="110"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="103"/>
+      <c r="K31" s="63"/>
       <c r="L31" s="105"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="59"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="63"/>
       <c r="O31" s="105"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="59"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="63"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13377,62 +13378,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13457,62 +13458,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
